--- a/حسابداری/بانک ها/رسالت ابوالفضل/1405/14050131-14050231.xlsx
+++ b/حسابداری/بانک ها/رسالت ابوالفضل/1405/14050131-14050231.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\بانک ها\رسالت ابوالفضل\1405\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\حسابداری باکسینو\حسابداری\بانک ها\رسالت ابوالفضل\1405\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED164FE4-3F3C-46BA-8B27-E9459EAEAB66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5D5F81C-5591-4694-8B91-7B1E137F9B50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="139">
   <si>
     <t>صورت حساب سپرده</t>
   </si>
@@ -439,6 +439,18 @@
   </si>
   <si>
     <t>60</t>
+  </si>
+  <si>
+    <t>1405/01/29</t>
+  </si>
+  <si>
+    <t>10:29:35</t>
+  </si>
+  <si>
+    <t>خريد کالا و خدمات با کارت 5041721220251467 متعلق به ابوالفضل شريفي ميناب (ابوالفضل شريفي ميناب) از پايانه فروش 8921247 - پذيرنده پایانه به پرداخت ملت - به پرداخت ملت - شماره مرجع 342368311753 شماره پيگيري 311753_سند تراکنش کارت</t>
+  </si>
+  <si>
+    <t>0</t>
   </si>
 </sst>
 </file>
@@ -487,7 +499,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -566,6 +578,24 @@
         <bgColor rgb="FFCCCCCC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FF8B8B8C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -594,7 +624,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -614,12 +644,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -683,6 +707,27 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="6" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1020,7 +1065,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I40"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="3" width="14" customWidth="1"/>
@@ -1035,30 +1080,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
+      <c r="A1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
     </row>
     <row r="2" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
     </row>
     <row r="3" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
@@ -2134,17 +2179,17 @@
       </c>
     </row>
     <row r="40" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="8" t="s">
+      <c r="A40" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="B40" s="8"/>
-      <c r="C40" s="8"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8"/>
-      <c r="G40" s="8"/>
-      <c r="H40" s="8"/>
-      <c r="I40" s="8"/>
+      <c r="B40" s="29"/>
+      <c r="C40" s="29"/>
+      <c r="D40" s="29"/>
+      <c r="E40" s="29"/>
+      <c r="F40" s="29"/>
+      <c r="G40" s="29"/>
+      <c r="H40" s="29"/>
+      <c r="I40" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2158,7 +2203,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D76E7258-BA94-4516-8A88-24D8DE23ACBA}">
-  <dimension ref="A1:P41"/>
+  <dimension ref="A1:P42"/>
   <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="20.25" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
@@ -2179,29 +2224,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
+      <c r="A1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
     </row>
     <row r="2" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
     </row>
     <row r="3" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
@@ -2228,1539 +2273,1577 @@
       <c r="H3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="K3" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="L3" s="9" t="s">
+      <c r="L3" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="M3" s="9" t="s">
+      <c r="M3" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="N3" s="9" t="s">
+      <c r="N3" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="O3" s="9" t="s">
+      <c r="O3" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="P3" s="9" t="s">
+      <c r="P3" s="7" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="20">
+    <row r="4" spans="1:16" s="30" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="B4" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="33" t="s">
+        <v>135</v>
+      </c>
+      <c r="D4" s="33" t="s">
+        <v>136</v>
+      </c>
+      <c r="E4" s="33" t="s">
+        <v>137</v>
+      </c>
+      <c r="F4" s="34">
+        <v>300000</v>
+      </c>
+      <c r="G4" s="34">
+        <v>0</v>
+      </c>
+      <c r="H4" s="34">
+        <v>48551116</v>
+      </c>
+      <c r="I4" s="24">
+        <v>11</v>
+      </c>
+      <c r="J4" s="24"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="24">
+        <v>91</v>
+      </c>
+      <c r="M4" s="24"/>
+      <c r="N4" s="24"/>
+      <c r="O4" s="32"/>
+      <c r="P4" s="32"/>
+    </row>
+    <row r="5" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="18">
         <v>1</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F5" s="8">
         <v>39000</v>
       </c>
-      <c r="G4" s="5">
-        <v>0</v>
-      </c>
-      <c r="H4" s="5">
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
         <v>48512116</v>
       </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="12">
-        <v>15</v>
-      </c>
-      <c r="N4" s="12">
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="10">
+        <v>15</v>
+      </c>
+      <c r="N5" s="10">
         <v>33</v>
       </c>
-      <c r="O4" s="12">
+      <c r="O5" s="10">
         <v>39000</v>
       </c>
-      <c r="P4" s="11" t="s">
+      <c r="P5" s="9" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="15">
-        <v>2</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="2" t="s">
+    <row r="6" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="13">
+        <v>2</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F6" s="11">
         <v>12200</v>
       </c>
-      <c r="G5" s="6">
-        <v>0</v>
-      </c>
-      <c r="H5" s="6">
+      <c r="G6" s="6">
+        <v>0</v>
+      </c>
+      <c r="H6" s="6">
         <v>48499916</v>
       </c>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="12">
-        <v>15</v>
-      </c>
-      <c r="N5" s="12">
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="10">
+        <v>15</v>
+      </c>
+      <c r="N6" s="10">
         <v>33</v>
       </c>
-      <c r="O5" s="12">
+      <c r="O6" s="10">
         <v>12200</v>
       </c>
-      <c r="P5" s="11" t="s">
+      <c r="P6" s="9" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="20">
+    <row r="7" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="18">
         <v>3</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="3" t="s">
+      <c r="B7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F7" s="8">
         <v>12500000</v>
       </c>
-      <c r="G6" s="5">
-        <v>0</v>
-      </c>
-      <c r="H6" s="5">
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
         <v>35999916</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I7" s="10">
         <v>17</v>
       </c>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="12">
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="10">
         <v>35</v>
       </c>
-      <c r="M6" s="11"/>
-      <c r="N6" s="11"/>
-      <c r="O6" s="11"/>
-      <c r="P6" s="11" t="s">
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="15">
+    <row r="8" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="13">
         <v>4</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="B8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F8" s="11">
         <v>220000</v>
       </c>
-      <c r="G7" s="6">
-        <v>0</v>
-      </c>
-      <c r="H7" s="6">
+      <c r="G8" s="6">
+        <v>0</v>
+      </c>
+      <c r="H8" s="6">
         <v>35779916</v>
       </c>
-      <c r="I7" s="12">
+      <c r="I8" s="10">
         <v>16</v>
       </c>
-      <c r="J7" s="11"/>
-      <c r="K7" s="11"/>
-      <c r="L7" s="12">
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="10">
         <v>34</v>
       </c>
-      <c r="M7" s="11"/>
-      <c r="N7" s="11"/>
-      <c r="O7" s="11"/>
-      <c r="P7" s="11" t="s">
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="9"/>
+      <c r="P8" s="9" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="20">
+    <row r="9" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="18">
         <v>5</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="3" t="s">
+      <c r="B9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E9" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F9" s="8">
         <v>4515000</v>
       </c>
-      <c r="G8" s="5">
-        <v>0</v>
-      </c>
-      <c r="H8" s="5">
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
         <v>31264916</v>
       </c>
-      <c r="I8" s="12">
+      <c r="I9" s="10">
         <v>18</v>
       </c>
-      <c r="J8" s="11"/>
-      <c r="K8" s="11"/>
-      <c r="L8" s="12">
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="10">
         <v>36</v>
       </c>
-      <c r="M8" s="11"/>
-      <c r="N8" s="11"/>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11" t="s">
+      <c r="M9" s="9"/>
+      <c r="N9" s="9"/>
+      <c r="O9" s="9"/>
+      <c r="P9" s="9" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="15">
+    <row r="10" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="13">
         <v>6</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="B10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F10" s="11">
         <v>14550000</v>
       </c>
-      <c r="G9" s="6">
-        <v>0</v>
-      </c>
-      <c r="H9" s="6">
+      <c r="G10" s="6">
+        <v>0</v>
+      </c>
+      <c r="H10" s="6">
         <v>16714916</v>
       </c>
-      <c r="I9" s="12">
+      <c r="I10" s="10">
         <v>22</v>
       </c>
-      <c r="J9" s="11"/>
-      <c r="K9" s="11"/>
-      <c r="L9" s="12">
+      <c r="J10" s="9"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="10">
         <v>40</v>
       </c>
-      <c r="M9" s="11"/>
-      <c r="N9" s="11"/>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11" t="s">
+      <c r="M10" s="9"/>
+      <c r="N10" s="9"/>
+      <c r="O10" s="9"/>
+      <c r="P10" s="9" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="20">
+    <row r="11" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="18">
         <v>7</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="3" t="s">
+      <c r="B11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E11" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F10" s="5">
-        <v>0</v>
-      </c>
-      <c r="G10" s="28">
+      <c r="F11" s="5">
+        <v>0</v>
+      </c>
+      <c r="G11" s="26">
         <v>100000000</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H11" s="5">
         <v>116714916</v>
       </c>
-      <c r="I10" s="11"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="27">
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="25">
         <v>26</v>
       </c>
-      <c r="L10" s="11"/>
-      <c r="M10" s="11"/>
-      <c r="N10" s="11"/>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11" t="s">
+      <c r="L11" s="9"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="9"/>
+      <c r="O11" s="9"/>
+      <c r="P11" s="9" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="15">
+    <row r="12" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="13">
         <v>8</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="B12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F11" s="6">
-        <v>0</v>
-      </c>
-      <c r="G11" s="13">
+      <c r="F12" s="6">
+        <v>0</v>
+      </c>
+      <c r="G12" s="11">
         <v>28770000</v>
       </c>
-      <c r="H11" s="6">
+      <c r="H12" s="6">
         <v>145484916</v>
       </c>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="12">
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="10">
         <v>31</v>
       </c>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="11"/>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11" t="s">
+      <c r="L12" s="9"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="9"/>
+      <c r="O12" s="9"/>
+      <c r="P12" s="9" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="20">
+    <row r="13" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="18">
         <v>9</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="3" t="s">
+      <c r="B13" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E13" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F13" s="8">
         <v>9000</v>
       </c>
-      <c r="G12" s="5">
-        <v>0</v>
-      </c>
-      <c r="H12" s="5">
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
         <v>145475916</v>
       </c>
-      <c r="I12" s="11"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="12">
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="10">
         <v>25</v>
       </c>
-      <c r="N12" s="12">
+      <c r="N13" s="10">
         <v>44</v>
       </c>
-      <c r="O12" s="12">
+      <c r="O13" s="10">
         <v>9000</v>
       </c>
-      <c r="P12" s="11" t="s">
+      <c r="P13" s="9" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="15">
+    <row r="14" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="13">
         <v>10</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="B14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F14" s="11">
         <v>2000000</v>
       </c>
-      <c r="G13" s="6">
-        <v>0</v>
-      </c>
-      <c r="H13" s="6">
+      <c r="G14" s="6">
+        <v>0</v>
+      </c>
+      <c r="H14" s="6">
         <v>143475916</v>
       </c>
-      <c r="I13" s="12">
+      <c r="I14" s="10">
         <v>21</v>
       </c>
-      <c r="J13" s="11"/>
-      <c r="K13" s="11"/>
-      <c r="L13" s="12">
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="10">
         <v>39</v>
       </c>
-      <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
-      <c r="O13" s="11"/>
-      <c r="P13" s="11" t="s">
+      <c r="M14" s="9"/>
+      <c r="N14" s="9"/>
+      <c r="O14" s="9"/>
+      <c r="P14" s="9" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="20">
+    <row r="15" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="18">
         <v>11</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="3" t="s">
+      <c r="B15" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E15" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F14" s="10">
+      <c r="F15" s="8">
         <v>9000</v>
       </c>
-      <c r="G14" s="5">
-        <v>0</v>
-      </c>
-      <c r="H14" s="5">
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
         <v>143466916</v>
       </c>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="14" t="s">
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="N14" s="12">
+      <c r="N15" s="10">
         <v>45</v>
       </c>
-      <c r="O14" s="12">
+      <c r="O15" s="10">
         <v>900</v>
       </c>
-      <c r="P14" s="11" t="s">
+      <c r="P15" s="9" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="15">
+    <row r="16" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="13">
         <v>12</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="2" t="s">
+      <c r="B16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F16" s="11">
         <v>1500000</v>
       </c>
-      <c r="G15" s="6">
-        <v>0</v>
-      </c>
-      <c r="H15" s="6">
+      <c r="G16" s="6">
+        <v>0</v>
+      </c>
+      <c r="H16" s="6">
         <v>141966916</v>
       </c>
-      <c r="I15" s="15" t="s">
+      <c r="I16" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="15" t="s">
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="M15" s="2"/>
-      <c r="N15" s="6"/>
-      <c r="O15" s="6"/>
-      <c r="P15" s="6" t="s">
+      <c r="M16" s="2"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="6"/>
+      <c r="P16" s="6" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="20">
+    <row r="17" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="18">
         <v>13</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" s="3" t="s">
+      <c r="B17" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E17" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F16" s="10">
+      <c r="F17" s="8">
         <v>5458000</v>
       </c>
-      <c r="G16" s="5">
-        <v>0</v>
-      </c>
-      <c r="H16" s="5">
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
         <v>136508916</v>
       </c>
-      <c r="I16" s="24" t="s">
+      <c r="I17" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="J16" s="19"/>
-      <c r="K16" s="19"/>
-      <c r="L16" s="25" t="s">
+      <c r="J17" s="17"/>
+      <c r="K17" s="17"/>
+      <c r="L17" s="23" t="s">
         <v>133</v>
       </c>
-      <c r="M16" s="16"/>
-      <c r="N16" s="16"/>
-      <c r="O16" s="16"/>
-      <c r="P16" s="25" t="s">
+      <c r="M17" s="14"/>
+      <c r="N17" s="14"/>
+      <c r="O17" s="14"/>
+      <c r="P17" s="23" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="15">
+    <row r="18" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="13">
         <v>14</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" s="2" t="s">
+      <c r="B18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D18" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E18" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F17" s="13">
+      <c r="F18" s="11">
         <v>1180000</v>
       </c>
-      <c r="G17" s="6">
-        <v>0</v>
-      </c>
-      <c r="H17" s="6">
+      <c r="G18" s="6">
+        <v>0</v>
+      </c>
+      <c r="H18" s="6">
         <v>135328916</v>
       </c>
-      <c r="I17" s="15" t="s">
+      <c r="I18" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="J17" s="16"/>
-      <c r="K17" s="16"/>
-      <c r="L17" s="17">
+      <c r="J18" s="14"/>
+      <c r="K18" s="14"/>
+      <c r="L18" s="15">
         <v>48</v>
       </c>
-      <c r="M17" s="16"/>
-      <c r="N17" s="16"/>
-      <c r="O17" s="16"/>
-      <c r="P17" s="18" t="s">
+      <c r="M18" s="14"/>
+      <c r="N18" s="14"/>
+      <c r="O18" s="14"/>
+      <c r="P18" s="16" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="20">
-        <v>15</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18" s="3" t="s">
+    <row r="19" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="18">
+        <v>15</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D19" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="E19" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F18" s="10">
+      <c r="F19" s="8">
         <v>9000</v>
       </c>
-      <c r="G18" s="5">
-        <v>0</v>
-      </c>
-      <c r="H18" s="5">
+      <c r="G19" s="5">
+        <v>0</v>
+      </c>
+      <c r="H19" s="5">
         <v>135319916</v>
       </c>
-      <c r="I18" s="1"/>
-      <c r="J18" s="16"/>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="17">
+      <c r="I19" s="1"/>
+      <c r="J19" s="14"/>
+      <c r="K19" s="14"/>
+      <c r="L19" s="14"/>
+      <c r="M19" s="15">
         <v>32</v>
       </c>
-      <c r="N18" s="17">
+      <c r="N19" s="15">
         <v>51</v>
       </c>
-      <c r="O18" s="17">
+      <c r="O19" s="15">
         <v>900</v>
       </c>
-      <c r="P18" s="18" t="s">
+      <c r="P19" s="16" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="15">
+    <row r="20" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="13">
         <v>16</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="2" t="s">
+      <c r="B20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D20" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E20" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="F19" s="13">
+      <c r="F20" s="11">
         <v>6000000</v>
       </c>
-      <c r="G19" s="6">
-        <v>0</v>
-      </c>
-      <c r="H19" s="6">
+      <c r="G20" s="6">
+        <v>0</v>
+      </c>
+      <c r="H20" s="6">
         <v>129319916</v>
       </c>
-      <c r="I19" s="15" t="s">
+      <c r="I20" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="J19" s="16"/>
-      <c r="K19" s="16"/>
-      <c r="L19" s="17">
+      <c r="J20" s="14"/>
+      <c r="K20" s="14"/>
+      <c r="L20" s="15">
         <v>49</v>
       </c>
-      <c r="M19" s="16"/>
-      <c r="N19" s="16"/>
-      <c r="O19" s="16"/>
-      <c r="P19" s="18" t="s">
+      <c r="M20" s="14"/>
+      <c r="N20" s="14"/>
+      <c r="O20" s="14"/>
+      <c r="P20" s="16" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="20">
+    <row r="21" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="18">
         <v>17</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="3" t="s">
+      <c r="B21" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E21" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F20" s="10">
+      <c r="F21" s="8">
         <v>18600</v>
       </c>
-      <c r="G20" s="5">
-        <v>0</v>
-      </c>
-      <c r="H20" s="5">
+      <c r="G21" s="5">
+        <v>0</v>
+      </c>
+      <c r="H21" s="5">
         <v>129301316</v>
       </c>
-      <c r="I20" s="1"/>
-      <c r="J20" s="16"/>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="17">
+      <c r="I21" s="1"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="14"/>
+      <c r="L21" s="14"/>
+      <c r="M21" s="15">
         <v>32</v>
       </c>
-      <c r="N20" s="17">
+      <c r="N21" s="15">
         <v>51</v>
       </c>
-      <c r="O20" s="17">
+      <c r="O21" s="15">
         <v>18600</v>
       </c>
-      <c r="P20" s="18" t="s">
+      <c r="P21" s="16" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="15">
+    <row r="22" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="13">
         <v>18</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C21" s="2" t="s">
+      <c r="B22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D22" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="E22" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="F21" s="13">
+      <c r="F22" s="11">
         <v>38800000</v>
       </c>
-      <c r="G21" s="6">
-        <v>0</v>
-      </c>
-      <c r="H21" s="6">
+      <c r="G22" s="6">
+        <v>0</v>
+      </c>
+      <c r="H22" s="6">
         <v>90501316</v>
       </c>
-      <c r="I21" s="15" t="s">
+      <c r="I22" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="J21" s="16"/>
-      <c r="K21" s="16"/>
-      <c r="L21" s="17">
+      <c r="J22" s="14"/>
+      <c r="K22" s="14"/>
+      <c r="L22" s="15">
         <v>50</v>
       </c>
-      <c r="M21" s="16"/>
-      <c r="N21" s="16"/>
-      <c r="O21" s="16"/>
-      <c r="P21" s="18" t="s">
+      <c r="M22" s="14"/>
+      <c r="N22" s="14"/>
+      <c r="O22" s="14"/>
+      <c r="P22" s="16" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="20">
+    <row r="23" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="18">
         <v>19</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B23" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C23" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D23" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="E23" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="F22" s="10">
+      <c r="F23" s="8">
         <v>41520</v>
       </c>
-      <c r="G22" s="5">
-        <v>0</v>
-      </c>
-      <c r="H22" s="5">
+      <c r="G23" s="5">
+        <v>0</v>
+      </c>
+      <c r="H23" s="5">
         <v>90459796</v>
       </c>
-      <c r="I22" s="1"/>
-      <c r="J22" s="16"/>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="17">
+      <c r="I23" s="1"/>
+      <c r="J23" s="14"/>
+      <c r="K23" s="14"/>
+      <c r="L23" s="14"/>
+      <c r="M23" s="15">
         <v>32</v>
       </c>
-      <c r="N22" s="17">
+      <c r="N23" s="15">
         <v>51</v>
       </c>
-      <c r="O22" s="17">
+      <c r="O23" s="15">
         <v>41520</v>
       </c>
-      <c r="P22" s="18" t="s">
+      <c r="P23" s="16" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="15">
+    <row r="24" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="13">
         <v>20</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C23" s="2" t="s">
+      <c r="B24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D24" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="E24" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F23" s="13">
+      <c r="F24" s="11">
         <v>1788000</v>
       </c>
-      <c r="G23" s="6">
-        <v>0</v>
-      </c>
-      <c r="H23" s="6">
+      <c r="G24" s="6">
+        <v>0</v>
+      </c>
+      <c r="H24" s="6">
         <v>88671796</v>
       </c>
-      <c r="I23" s="15" t="s">
+      <c r="I24" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="J23" s="19"/>
-      <c r="K23" s="19"/>
-      <c r="L23" s="17">
+      <c r="J24" s="17"/>
+      <c r="K24" s="17"/>
+      <c r="L24" s="15">
         <v>53</v>
       </c>
-      <c r="M23" s="19"/>
-      <c r="N23" s="19"/>
-      <c r="O23" s="19"/>
-      <c r="P23" s="19" t="s">
+      <c r="M24" s="17"/>
+      <c r="N24" s="17"/>
+      <c r="O24" s="17"/>
+      <c r="P24" s="17" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="20">
+    <row r="25" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="18">
         <v>21</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C24" s="3" t="s">
+      <c r="B25" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D25" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="E25" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F24" s="10">
+      <c r="F25" s="8">
         <v>9000</v>
       </c>
-      <c r="G24" s="5">
-        <v>0</v>
-      </c>
-      <c r="H24" s="5">
+      <c r="G25" s="5">
+        <v>0</v>
+      </c>
+      <c r="H25" s="5">
         <v>88662796</v>
       </c>
-      <c r="I24" s="1"/>
-      <c r="J24" s="19"/>
-      <c r="K24" s="19"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="17">
+      <c r="I25" s="1"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="17"/>
+      <c r="L25" s="14"/>
+      <c r="M25" s="15">
         <v>33</v>
       </c>
-      <c r="N24" s="17">
+      <c r="N25" s="15">
         <v>52</v>
       </c>
-      <c r="O24" s="17">
+      <c r="O25" s="15">
         <v>9000</v>
       </c>
-      <c r="P24" s="19" t="s">
+      <c r="P25" s="17" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="15">
+    <row r="26" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="13">
         <v>22</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C25" s="2" t="s">
+      <c r="B26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D26" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E26" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F25" s="13">
+      <c r="F26" s="11">
         <v>6000000</v>
       </c>
-      <c r="G25" s="6">
-        <v>0</v>
-      </c>
-      <c r="H25" s="6">
+      <c r="G26" s="6">
+        <v>0</v>
+      </c>
+      <c r="H26" s="6">
         <v>82662796</v>
       </c>
-      <c r="I25" s="15" t="s">
+      <c r="I26" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="J25" s="19"/>
-      <c r="K25" s="19"/>
-      <c r="L25" s="17">
+      <c r="J26" s="17"/>
+      <c r="K26" s="17"/>
+      <c r="L26" s="15">
         <v>54</v>
       </c>
-      <c r="M25" s="19"/>
-      <c r="N25" s="19"/>
-      <c r="O25" s="19"/>
-      <c r="P25" s="19" t="s">
+      <c r="M26" s="17"/>
+      <c r="N26" s="17"/>
+      <c r="O26" s="17"/>
+      <c r="P26" s="17" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="20">
+    <row r="27" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="18">
         <v>23</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C26" s="3" t="s">
+      <c r="B27" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="D27" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="E27" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F26" s="10">
+      <c r="F27" s="8">
         <v>3800000</v>
       </c>
-      <c r="G26" s="5">
-        <v>0</v>
-      </c>
-      <c r="H26" s="5">
+      <c r="G27" s="5">
+        <v>0</v>
+      </c>
+      <c r="H27" s="5">
         <v>78862796</v>
       </c>
-      <c r="I26" s="20" t="s">
+      <c r="I27" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="J26" s="19"/>
-      <c r="K26" s="19"/>
-      <c r="L26" s="17">
+      <c r="J27" s="17"/>
+      <c r="K27" s="17"/>
+      <c r="L27" s="15">
         <v>57</v>
       </c>
-      <c r="M26" s="19"/>
-      <c r="N26" s="19"/>
-      <c r="O26" s="19"/>
-      <c r="P26" s="21" t="s">
+      <c r="M27" s="17"/>
+      <c r="N27" s="17"/>
+      <c r="O27" s="17"/>
+      <c r="P27" s="19" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="15">
+    <row r="28" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="13">
         <v>24</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C27" s="2" t="s">
+      <c r="B28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D28" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E28" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F27" s="13">
+      <c r="F28" s="11">
         <v>9000</v>
       </c>
-      <c r="G27" s="6">
-        <v>0</v>
-      </c>
-      <c r="H27" s="6">
+      <c r="G28" s="6">
+        <v>0</v>
+      </c>
+      <c r="H28" s="6">
         <v>78853796</v>
       </c>
-      <c r="I27" s="1"/>
-      <c r="J27" s="19"/>
-      <c r="K27" s="19"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="17">
+      <c r="I28" s="1"/>
+      <c r="J28" s="17"/>
+      <c r="K28" s="17"/>
+      <c r="L28" s="14"/>
+      <c r="M28" s="15">
         <v>33</v>
       </c>
-      <c r="N27" s="17">
+      <c r="N28" s="15">
         <v>52</v>
       </c>
-      <c r="O27" s="17">
+      <c r="O28" s="15">
         <v>9000</v>
       </c>
-      <c r="P27" s="19" t="s">
+      <c r="P28" s="17" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="20">
+    <row r="29" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="18">
         <v>25</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C28" s="3" t="s">
+      <c r="B29" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="D29" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="E29" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F28" s="10">
+      <c r="F29" s="8">
         <v>1962620</v>
       </c>
-      <c r="G28" s="5">
-        <v>0</v>
-      </c>
-      <c r="H28" s="5">
+      <c r="G29" s="5">
+        <v>0</v>
+      </c>
+      <c r="H29" s="5">
         <v>76891176</v>
       </c>
-      <c r="I28" s="20" t="s">
+      <c r="I29" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="J28" s="19"/>
-      <c r="K28" s="19"/>
-      <c r="L28" s="17">
+      <c r="J29" s="17"/>
+      <c r="K29" s="17"/>
+      <c r="L29" s="15">
         <v>56</v>
       </c>
-      <c r="M28" s="19"/>
-      <c r="N28" s="19"/>
-      <c r="O28" s="19"/>
-      <c r="P28" s="19" t="s">
+      <c r="M29" s="17"/>
+      <c r="N29" s="17"/>
+      <c r="O29" s="17"/>
+      <c r="P29" s="17" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="15">
+    <row r="30" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="13">
         <v>26</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C29" s="2" t="s">
+      <c r="B30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D30" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="E30" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="F29" s="13">
+      <c r="F30" s="11">
         <v>825000</v>
       </c>
-      <c r="G29" s="6">
-        <v>0</v>
-      </c>
-      <c r="H29" s="6">
+      <c r="G30" s="6">
+        <v>0</v>
+      </c>
+      <c r="H30" s="6">
         <v>76066176</v>
       </c>
-      <c r="I29" s="22" t="s">
+      <c r="I30" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="J29" s="19"/>
-      <c r="K29" s="19"/>
-      <c r="L29" s="17">
+      <c r="J30" s="17"/>
+      <c r="K30" s="17"/>
+      <c r="L30" s="15">
         <v>59</v>
       </c>
-      <c r="M29" s="19"/>
-      <c r="N29" s="19"/>
-      <c r="O29" s="19"/>
-      <c r="P29" s="19" t="s">
+      <c r="M30" s="17"/>
+      <c r="N30" s="17"/>
+      <c r="O30" s="17"/>
+      <c r="P30" s="17" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="20">
+    <row r="31" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="18">
         <v>27</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C30" s="3" t="s">
+      <c r="B31" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="D31" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="E31" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="F30" s="10">
+      <c r="F31" s="8">
         <v>600000</v>
       </c>
-      <c r="G30" s="5">
-        <v>0</v>
-      </c>
-      <c r="H30" s="5">
+      <c r="G31" s="5">
+        <v>0</v>
+      </c>
+      <c r="H31" s="5">
         <v>75466176</v>
       </c>
-      <c r="I30" s="24" t="s">
+      <c r="I31" s="22" t="s">
         <v>119</v>
       </c>
-      <c r="J30" s="16"/>
-      <c r="K30" s="16"/>
-      <c r="L30" s="17">
+      <c r="J31" s="14"/>
+      <c r="K31" s="14"/>
+      <c r="L31" s="15">
         <v>87</v>
       </c>
-      <c r="M30" s="16"/>
-      <c r="N30" s="16"/>
-      <c r="O30" s="16"/>
-      <c r="P30" s="18" t="s">
+      <c r="M31" s="14"/>
+      <c r="N31" s="14"/>
+      <c r="O31" s="14"/>
+      <c r="P31" s="16" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="15">
+    <row r="32" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="13">
         <v>28</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C31" s="2" t="s">
+      <c r="B32" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D32" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="E32" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F31" s="13">
+      <c r="F32" s="11">
         <v>9000</v>
       </c>
-      <c r="G31" s="6">
-        <v>0</v>
-      </c>
-      <c r="H31" s="6">
+      <c r="G32" s="6">
+        <v>0</v>
+      </c>
+      <c r="H32" s="6">
         <v>75457176</v>
       </c>
-      <c r="I31" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="J31" s="16"/>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="17">
+      <c r="I32" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="J32" s="14"/>
+      <c r="K32" s="14"/>
+      <c r="L32" s="14"/>
+      <c r="M32" s="15">
         <v>57</v>
       </c>
-      <c r="N31" s="17">
+      <c r="N32" s="15">
         <v>89</v>
       </c>
-      <c r="O31" s="17">
+      <c r="O32" s="15">
         <v>9000</v>
       </c>
-      <c r="P31" s="18" t="s">
+      <c r="P32" s="16" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="20">
+    <row r="33" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="18">
         <v>29</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C32" s="3" t="s">
+      <c r="B33" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="D33" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E32" s="3" t="s">
+      <c r="E33" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F32" s="10">
+      <c r="F33" s="8">
         <v>2500000</v>
       </c>
-      <c r="G32" s="5">
-        <v>0</v>
-      </c>
-      <c r="H32" s="5">
+      <c r="G33" s="5">
+        <v>0</v>
+      </c>
+      <c r="H33" s="5">
         <v>72957176</v>
       </c>
-      <c r="I32" s="24" t="s">
+      <c r="I33" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="J32" s="16"/>
-      <c r="K32" s="16"/>
-      <c r="L32" s="17">
+      <c r="J33" s="14"/>
+      <c r="K33" s="14"/>
+      <c r="L33" s="15">
         <v>67</v>
       </c>
-      <c r="M32" s="16"/>
-      <c r="N32" s="16"/>
-      <c r="O32" s="16"/>
-      <c r="P32" s="18" t="s">
+      <c r="M33" s="14"/>
+      <c r="N33" s="14"/>
+      <c r="O33" s="14"/>
+      <c r="P33" s="16" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="15">
+    <row r="34" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="13">
         <v>30</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C33" s="2" t="s">
+      <c r="B34" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D34" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="E34" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="F33" s="13">
+      <c r="F34" s="11">
         <v>5650000</v>
       </c>
-      <c r="G33" s="6">
-        <v>0</v>
-      </c>
-      <c r="H33" s="6">
+      <c r="G34" s="6">
+        <v>0</v>
+      </c>
+      <c r="H34" s="6">
         <v>67307176</v>
       </c>
-      <c r="I33" s="22" t="s">
+      <c r="I34" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="J33" s="16"/>
-      <c r="K33" s="16"/>
-      <c r="L33" s="17">
+      <c r="J34" s="14"/>
+      <c r="K34" s="14"/>
+      <c r="L34" s="15">
         <v>69</v>
       </c>
-      <c r="M33" s="16"/>
-      <c r="N33" s="16"/>
-      <c r="O33" s="16"/>
-      <c r="P33" s="18" t="s">
+      <c r="M34" s="14"/>
+      <c r="N34" s="14"/>
+      <c r="O34" s="14"/>
+      <c r="P34" s="16" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="20">
+    <row r="35" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="18">
         <v>31</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C34" s="3" t="s">
+      <c r="B35" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="D35" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="E34" s="3" t="s">
+      <c r="E35" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="F34" s="10">
+      <c r="F35" s="8">
         <v>1788012</v>
       </c>
-      <c r="G34" s="5">
-        <v>0</v>
-      </c>
-      <c r="H34" s="5">
+      <c r="G35" s="5">
+        <v>0</v>
+      </c>
+      <c r="H35" s="5">
         <v>65519164</v>
       </c>
-      <c r="I34" s="24" t="s">
+      <c r="I35" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="J34" s="16"/>
-      <c r="K34" s="16"/>
-      <c r="L34" s="17">
+      <c r="J35" s="14"/>
+      <c r="K35" s="14"/>
+      <c r="L35" s="15">
         <v>70</v>
       </c>
-      <c r="M34" s="16"/>
-      <c r="N34" s="16"/>
-      <c r="O34" s="16"/>
-      <c r="P34" s="18" t="s">
+      <c r="M35" s="14"/>
+      <c r="N35" s="14"/>
+      <c r="O35" s="14"/>
+      <c r="P35" s="16" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="15">
+    <row r="36" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A36" s="13">
         <v>32</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C35" s="2" t="s">
+      <c r="B36" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="D36" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="E36" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F35" s="13">
+      <c r="F36" s="11">
         <v>9000</v>
       </c>
-      <c r="G35" s="6">
-        <v>0</v>
-      </c>
-      <c r="H35" s="6">
+      <c r="G36" s="6">
+        <v>0</v>
+      </c>
+      <c r="H36" s="6">
         <v>65510164</v>
       </c>
-      <c r="I35" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="J35" s="16"/>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="17">
+      <c r="I36" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="J36" s="14"/>
+      <c r="K36" s="14"/>
+      <c r="L36" s="14"/>
+      <c r="M36" s="15">
         <v>57</v>
       </c>
-      <c r="N35" s="17">
+      <c r="N36" s="15">
         <v>89</v>
       </c>
-      <c r="O35" s="17">
+      <c r="O36" s="15">
         <v>9000</v>
       </c>
-      <c r="P35" s="18" t="s">
+      <c r="P36" s="16" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="20">
+    <row r="37" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A37" s="18">
         <v>33</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C36" s="3" t="s">
+      <c r="B37" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="D37" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="E36" s="3" t="s">
+      <c r="E37" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="F36" s="10">
+      <c r="F37" s="8">
         <v>9000000</v>
       </c>
-      <c r="G36" s="5">
-        <v>0</v>
-      </c>
-      <c r="H36" s="5">
+      <c r="G37" s="5">
+        <v>0</v>
+      </c>
+      <c r="H37" s="5">
         <v>56510164</v>
       </c>
-      <c r="I36" s="24" t="s">
+      <c r="I37" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="J36" s="16"/>
-      <c r="K36" s="16"/>
-      <c r="L36" s="17">
+      <c r="J37" s="14"/>
+      <c r="K37" s="14"/>
+      <c r="L37" s="15">
         <v>71</v>
       </c>
-      <c r="M36" s="16"/>
-      <c r="N36" s="16"/>
-      <c r="O36" s="16"/>
-      <c r="P36" s="18" t="s">
+      <c r="M37" s="14"/>
+      <c r="N37" s="14"/>
+      <c r="O37" s="14"/>
+      <c r="P37" s="16" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="15">
+    <row r="38" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A38" s="13">
         <v>34</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C37" s="2" t="s">
+      <c r="B38" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="D38" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="E38" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F37" s="13">
+      <c r="F38" s="11">
         <v>9000</v>
       </c>
-      <c r="G37" s="6">
-        <v>0</v>
-      </c>
-      <c r="H37" s="6">
+      <c r="G38" s="6">
+        <v>0</v>
+      </c>
+      <c r="H38" s="6">
         <v>56501164</v>
       </c>
-      <c r="I37" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="J37" s="16"/>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="17">
+      <c r="I38" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="J38" s="14"/>
+      <c r="K38" s="14"/>
+      <c r="L38" s="14"/>
+      <c r="M38" s="15">
         <v>57</v>
       </c>
-      <c r="N37" s="17">
+      <c r="N38" s="15">
         <v>89</v>
       </c>
-      <c r="O37" s="17">
+      <c r="O38" s="15">
         <v>9000</v>
       </c>
-      <c r="P37" s="18" t="s">
+      <c r="P38" s="16" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="20">
+    <row r="39" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A39" s="18">
         <v>35</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C38" s="3" t="s">
+      <c r="B39" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="D39" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E38" s="3" t="s">
+      <c r="E39" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="F38" s="10">
+      <c r="F39" s="8">
         <v>6000000</v>
       </c>
-      <c r="G38" s="5">
-        <v>0</v>
-      </c>
-      <c r="H38" s="5">
+      <c r="G39" s="5">
+        <v>0</v>
+      </c>
+      <c r="H39" s="5">
         <v>50501164</v>
       </c>
-      <c r="I38" s="24" t="s">
+      <c r="I39" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="J38" s="16"/>
-      <c r="K38" s="16"/>
-      <c r="L38" s="17">
+      <c r="J39" s="14"/>
+      <c r="K39" s="14"/>
+      <c r="L39" s="15">
         <v>72</v>
       </c>
-      <c r="M38" s="16"/>
-      <c r="N38" s="16"/>
-      <c r="O38" s="16"/>
-      <c r="P38" s="18" t="s">
+      <c r="M39" s="14"/>
+      <c r="N39" s="14"/>
+      <c r="O39" s="14"/>
+      <c r="P39" s="16" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="39" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="15">
+    <row r="40" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A40" s="13">
         <v>36</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C39" s="2" t="s">
+      <c r="B40" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="D40" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E39" s="2" t="s">
+      <c r="E40" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="F39" s="13">
+      <c r="F40" s="11">
         <v>2050000</v>
       </c>
-      <c r="G39" s="6">
-        <v>0</v>
-      </c>
-      <c r="H39" s="6">
+      <c r="G40" s="6">
+        <v>0</v>
+      </c>
+      <c r="H40" s="6">
         <v>48451164</v>
       </c>
-      <c r="I39" s="22" t="s">
+      <c r="I40" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="J39" s="16"/>
-      <c r="K39" s="16"/>
-      <c r="L39" s="17">
+      <c r="J40" s="14"/>
+      <c r="K40" s="14"/>
+      <c r="L40" s="15">
         <v>88</v>
       </c>
-      <c r="M39" s="16"/>
-      <c r="N39" s="16"/>
-      <c r="O39" s="16"/>
-      <c r="P39" s="18" t="s">
+      <c r="M40" s="14"/>
+      <c r="N40" s="14"/>
+      <c r="O40" s="14"/>
+      <c r="P40" s="16" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="40" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="26"/>
-      <c r="B40" s="26"/>
-      <c r="C40" s="26"/>
-      <c r="D40" s="26"/>
-      <c r="E40" s="26"/>
-      <c r="F40" s="29">
-        <f>SUM(F4:F39)</f>
+    <row r="41" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A41" s="24"/>
+      <c r="B41" s="24"/>
+      <c r="C41" s="24"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="24"/>
+      <c r="F41" s="27">
+        <f>SUM(F5:F40)</f>
         <v>128869952</v>
       </c>
-      <c r="G40" s="29">
-        <f>SUM(G4:G39)</f>
+      <c r="G41" s="27">
+        <f>SUM(G5:G40)</f>
         <v>128770000</v>
       </c>
-      <c r="H40" s="26"/>
-      <c r="I40" s="26"/>
-      <c r="J40" s="26"/>
-      <c r="K40" s="26"/>
-      <c r="L40" s="26"/>
-      <c r="M40" s="26"/>
-      <c r="N40" s="26"/>
-      <c r="O40" s="26"/>
-      <c r="P40" s="26"/>
-    </row>
-    <row r="41" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="E41" s="8" t="s">
+      <c r="H41" s="24"/>
+      <c r="I41" s="24"/>
+      <c r="J41" s="24"/>
+      <c r="K41" s="24"/>
+      <c r="L41" s="24"/>
+      <c r="M41" s="24"/>
+      <c r="N41" s="24"/>
+      <c r="O41" s="24"/>
+      <c r="P41" s="24"/>
+    </row>
+    <row r="42" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E42" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="F41" s="8"/>
-      <c r="G41" s="8"/>
-      <c r="H41" s="8"/>
-      <c r="I41" s="8"/>
-      <c r="J41" s="8"/>
-      <c r="K41" s="8"/>
-      <c r="L41" s="8"/>
-      <c r="M41" s="8"/>
+      <c r="F42" s="29"/>
+      <c r="G42" s="29"/>
+      <c r="H42" s="29"/>
+      <c r="I42" s="29"/>
+      <c r="J42" s="29"/>
+      <c r="K42" s="29"/>
+      <c r="L42" s="29"/>
+      <c r="M42" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="E41:M41"/>
+    <mergeCell ref="E42:M42"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/حسابداری/بانک ها/رسالت ابوالفضل/1405/14050131-14050231.xlsx
+++ b/حسابداری/بانک ها/رسالت ابوالفضل/1405/14050131-14050231.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\حسابداری باکسینو\حسابداری\بانک ها\رسالت ابوالفضل\1405\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5D5F81C-5591-4694-8B91-7B1E137F9B50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60B95E2D-75D8-408F-9F16-4E2D760B7628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -709,12 +709,6 @@
     <xf numFmtId="3" fontId="6" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -728,6 +722,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1080,30 +1080,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
+      <c r="A1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
     </row>
     <row r="2" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
     </row>
     <row r="3" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
@@ -2179,17 +2179,17 @@
       </c>
     </row>
     <row r="40" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="29" t="s">
+      <c r="A40" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="B40" s="29"/>
-      <c r="C40" s="29"/>
-      <c r="D40" s="29"/>
-      <c r="E40" s="29"/>
-      <c r="F40" s="29"/>
-      <c r="G40" s="29"/>
-      <c r="H40" s="29"/>
-      <c r="I40" s="29"/>
+      <c r="B40" s="34"/>
+      <c r="C40" s="34"/>
+      <c r="D40" s="34"/>
+      <c r="E40" s="34"/>
+      <c r="F40" s="34"/>
+      <c r="G40" s="34"/>
+      <c r="H40" s="34"/>
+      <c r="I40" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2224,29 +2224,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
+      <c r="A1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
     </row>
     <row r="2" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
     </row>
     <row r="3" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
@@ -2298,29 +2298,29 @@
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:16" s="30" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="31" t="s">
+    <row r="4" spans="1:16" s="28" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="29" t="s">
         <v>138</v>
       </c>
-      <c r="B4" s="33" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="33" t="s">
+      <c r="B4" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="31" t="s">
         <v>135</v>
       </c>
-      <c r="D4" s="33" t="s">
+      <c r="D4" s="31" t="s">
         <v>136</v>
       </c>
-      <c r="E4" s="33" t="s">
+      <c r="E4" s="31" t="s">
         <v>137</v>
       </c>
-      <c r="F4" s="34">
+      <c r="F4" s="32">
         <v>300000</v>
       </c>
-      <c r="G4" s="34">
-        <v>0</v>
-      </c>
-      <c r="H4" s="34">
+      <c r="G4" s="32">
+        <v>0</v>
+      </c>
+      <c r="H4" s="32">
         <v>48551116</v>
       </c>
       <c r="I4" s="24">
@@ -2333,8 +2333,8 @@
       </c>
       <c r="M4" s="24"/>
       <c r="N4" s="24"/>
-      <c r="O4" s="32"/>
-      <c r="P4" s="32"/>
+      <c r="O4" s="30"/>
+      <c r="P4" s="30"/>
     </row>
     <row r="5" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="18">
@@ -2644,9 +2644,11 @@
         <v>145484916</v>
       </c>
       <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
+      <c r="J12" s="10">
+        <v>105</v>
+      </c>
       <c r="K12" s="10">
-        <v>31</v>
+        <v>168</v>
       </c>
       <c r="L12" s="9"/>
       <c r="M12" s="9"/>
@@ -3827,17 +3829,17 @@
       <c r="P41" s="24"/>
     </row>
     <row r="42" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="E42" s="29" t="s">
+      <c r="E42" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="F42" s="29"/>
-      <c r="G42" s="29"/>
-      <c r="H42" s="29"/>
-      <c r="I42" s="29"/>
-      <c r="J42" s="29"/>
-      <c r="K42" s="29"/>
-      <c r="L42" s="29"/>
-      <c r="M42" s="29"/>
+      <c r="F42" s="34"/>
+      <c r="G42" s="34"/>
+      <c r="H42" s="34"/>
+      <c r="I42" s="34"/>
+      <c r="J42" s="34"/>
+      <c r="K42" s="34"/>
+      <c r="L42" s="34"/>
+      <c r="M42" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="3">
